--- a/integra-ifood/relatorios/cadastrarEAN.xlsx
+++ b/integra-ifood/relatorios/cadastrarEAN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -406,32 +406,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>cod</v>
+        <v>Código PLU</v>
       </c>
       <c r="B1" t="str">
-        <v>name</v>
+        <v>Nome do Produto</v>
       </c>
       <c r="C1" t="str">
-        <v>ean</v>
+        <v>EAN</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>8243</v>
-      </c>
-      <c r="B2" t="str">
-        <v>FITA DUPLA FACE ACRILICA 12MMX2M</v>
-      </c>
       <c r="C2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>8535</v>
+        <v>3631</v>
       </c>
       <c r="B3" t="str">
-        <v>FITA DUPLA FACE ACRILICA 12MMX33M</v>
+        <v>LUVA PVC SOLD 20MM</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -439,10 +433,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>9104</v>
+        <v>4607</v>
       </c>
       <c r="B4" t="str">
-        <v>FITA DUPLA FACE ACRILICA 9MMX33M</v>
+        <v>LUVA PVC SOLD 25MM</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -450,10 +444,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>18953</v>
+        <v>4608</v>
       </c>
       <c r="B5" t="str">
-        <v>FITA EVA VEDACAO 10MMX7M</v>
+        <v>LUVA PVC SOLD 32MM</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -461,10 +455,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>18620</v>
+        <v>4606</v>
       </c>
       <c r="B6" t="str">
-        <v>ESCOVA VEDACAO 5MMX50M</v>
+        <v>LUVA PVC SOLD 20MM</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -472,10 +466,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>4098</v>
+        <v>4609</v>
       </c>
       <c r="B7" t="str">
-        <v>NOBREAK 600VA BIVOLT SAIDA 110VAC</v>
+        <v>CURVA PVC SOLD 25MM LONGA</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -483,10 +477,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>13243</v>
+        <v>2007</v>
       </c>
       <c r="B8" t="str">
-        <v>NOBREAK 1200VA SAIDA 110VAC</v>
+        <v>CURVA PVC SOLD 32MM</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -494,10 +488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>11394</v>
+        <v>3632</v>
       </c>
       <c r="B9" t="str">
-        <v>NOBREAK 2200VA BIVOLT SAIDA 110VAC</v>
+        <v>LUVA PVC SOLD 32MM</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -505,10 +499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18884</v>
+        <v>2245</v>
       </c>
       <c r="B10" t="str">
-        <v>NOBREAK 2000VA BIVOLT SAIDA 220VAC</v>
+        <v>CURVA PVC SOLD 20MM</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -516,10 +510,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>17865</v>
+        <v>2277</v>
       </c>
       <c r="B11" t="str">
-        <v>NOBREAK 1500VA BIVOLT SAIDA 220VAC</v>
+        <v>LUVA PVC SOLD 25MM</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -527,10 +521,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>17710</v>
+        <v>2249</v>
       </c>
       <c r="B12" t="str">
-        <v>NOBREAK 720VA BIVOLT SAIDA 220VAC</v>
+        <v>CURVA PVC SOLD 50MM</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -538,10 +532,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>17213</v>
+        <v>6329</v>
       </c>
       <c r="B13" t="str">
-        <v>NOBREAK 700VA 220VAC/220VAC</v>
+        <v>CURVA PVC SOLD 32MM</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -549,10 +543,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>17863</v>
+        <v>7516</v>
       </c>
       <c r="B14" t="str">
-        <v>NOBREAK 1200VA BIVOLT SAIDA 220VAC</v>
+        <v>CURVA PVC SOLD 25MM CURTA</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -560,10 +554,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>18584</v>
+        <v>17995</v>
       </c>
       <c r="B15" t="str">
-        <v>NOBREAK 1200VA BIVOLT SAIDA 110VAC</v>
+        <v>CURVA PVC SOLD 40MM</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -571,18 +565,40 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>17842</v>
+        <v>21469</v>
       </c>
       <c r="B16" t="str">
-        <v>NOBREAK 1200VA BIVOLT SAIDA 110VAC</v>
+        <v>ELETRODO CORTE PLASMA TOCHA</v>
       </c>
       <c r="C16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>21470</v>
+      </c>
+      <c r="B17" t="str">
+        <v>MAQUINA DE CORTE PLASMA MANUAL</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>21468</v>
+      </c>
+      <c r="B18" t="str">
+        <v>BICO DE CORTE TOCHA PLASMA 1.0MM</v>
+      </c>
+      <c r="C18" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
   </ignoredErrors>
 </worksheet>
 </file>